--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_median_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_median_a_2023_arica_y_parinacota.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:17</t>
+    <t xml:space="preserve">2026-09-09 21:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_median_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_median_a_2023_arica_y_parinacota.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:21</t>
+    <t xml:space="preserve">2026-09-18 09:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_median_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_median_a_2023_arica_y_parinacota.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:17</t>
+    <t xml:space="preserve">2026-09-25 21:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_median_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_median_a_2023_arica_y_parinacota.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:38</t>
+    <t xml:space="preserve">2026-10-05 02:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
